--- a/branches/feat/conformance-statements/all-profiles.xlsx
+++ b/branches/feat/conformance-statements/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:14:56+00:00</t>
+    <t>2026-07-26T12:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
